--- a/results/FigureData1.xlsx
+++ b/results/FigureData1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>file name</t>
   </si>
@@ -26,42 +26,9 @@
     <t>x-text</t>
   </si>
   <si>
-    <t>Week number</t>
-  </si>
-  <si>
     <t>x-labels</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -129,96 +96,6 @@
   </si>
   <si>
     <t>5-season average Norovirus laboratory reports</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>28.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>32.0</t>
-  </si>
-  <si>
-    <t>33.0</t>
-  </si>
-  <si>
-    <t>34.0</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>36.0</t>
-  </si>
-  <si>
-    <t>37.0</t>
-  </si>
-  <si>
-    <t>38.0</t>
-  </si>
-  <si>
-    <t>39.0</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
-    <t>41.0</t>
-  </si>
-  <si>
-    <t>42.0</t>
-  </si>
-  <si>
-    <t>43.0</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>45.0</t>
-  </si>
-  <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>47.0</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>34.66666666666667</t>
-  </si>
-  <si>
-    <t>18.333333333333336</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
   </si>
   <si>
     <t>5.0</t>
@@ -665,10 +542,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:BA11"/>
+  <dimension ref="A2:W11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -676,449 +553,236 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:53">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" t="s">
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="J4" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="K4" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="L4" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="M4" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="N4" t="s">
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="O4" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="P4" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="R4" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="S4" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:53">
-      <c r="A5" t="s">
+      <c r="G6" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:53">
-      <c r="A6" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F9" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:53">
-      <c r="A7" t="s">
+      <c r="K9" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="L9" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:53">
-      <c r="B9" t="s">
+      <c r="M9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="N9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="O9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="P9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="Q9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
+      <c r="R9" t="s">
         <v>43</v>
       </c>
-      <c r="H9" t="s">
+      <c r="S9" t="s">
         <v>44</v>
       </c>
-      <c r="I9" t="s">
+      <c r="T9" t="s">
         <v>45</v>
       </c>
-      <c r="J9" t="s">
+      <c r="U9" t="s">
         <v>46</v>
       </c>
-      <c r="K9" t="s">
+      <c r="V9" t="s">
         <v>47</v>
       </c>
-      <c r="L9" t="s">
+      <c r="W9" t="s">
         <v>48</v>
       </c>
-      <c r="M9" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" t="s">
-        <v>55</v>
-      </c>
-      <c r="T9" t="s">
-        <v>56</v>
-      </c>
-      <c r="U9" t="s">
-        <v>57</v>
-      </c>
-      <c r="V9" t="s">
-        <v>58</v>
-      </c>
-      <c r="W9" t="s">
-        <v>59</v>
-      </c>
-      <c r="X9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:53">
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>582.1</v>
       </c>
       <c r="C10">
-        <v>88.40000000000001</v>
+        <v>612.6</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>551.6</v>
       </c>
       <c r="E10">
-        <v>88.40000000000001</v>
+        <v>515.8</v>
       </c>
       <c r="F10">
-        <v>88.40000000000001</v>
+        <v>550.5</v>
       </c>
       <c r="G10">
-        <v>82.09999999999999</v>
+        <v>427.4</v>
       </c>
       <c r="H10">
-        <v>84.2</v>
+        <v>323.2</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>363.2</v>
       </c>
       <c r="J10">
-        <v>68.40000000000001</v>
+        <v>406.3</v>
       </c>
       <c r="K10">
-        <v>61.1</v>
+        <v>397.9</v>
       </c>
       <c r="L10">
-        <v>68.40000000000001</v>
+        <v>332.6</v>
       </c>
       <c r="M10">
-        <v>65.3</v>
+        <v>382.1</v>
       </c>
       <c r="N10">
-        <v>73.7</v>
+        <v>314.7</v>
       </c>
       <c r="O10">
-        <v>97.90000000000001</v>
+        <v>348.4</v>
       </c>
       <c r="P10">
-        <v>112.6</v>
+        <v>260</v>
       </c>
       <c r="Q10">
-        <v>154.7</v>
+        <v>303.2</v>
       </c>
       <c r="R10">
-        <v>135.8</v>
+        <v>278.9</v>
       </c>
       <c r="S10">
-        <v>152.6</v>
+        <v>128.4</v>
       </c>
       <c r="T10">
-        <v>168.4</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>153.7</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>150.5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>238.9</v>
-      </c>
-      <c r="X10">
-        <v>307.4</v>
-      </c>
-      <c r="Y10">
-        <v>277.9</v>
-      </c>
-      <c r="Z10">
-        <v>253.7</v>
-      </c>
-      <c r="AA10">
-        <v>217.9</v>
-      </c>
-      <c r="AB10">
-        <v>343.2</v>
-      </c>
-      <c r="AC10">
-        <v>520</v>
-      </c>
-      <c r="AD10">
-        <v>621.1</v>
-      </c>
-      <c r="AE10">
-        <v>604.2</v>
-      </c>
-      <c r="AF10">
-        <v>582.1</v>
-      </c>
-      <c r="AG10">
-        <v>612.6</v>
-      </c>
-      <c r="AH10">
-        <v>551.6</v>
-      </c>
-      <c r="AI10">
-        <v>515.8</v>
-      </c>
-      <c r="AJ10">
-        <v>550.5</v>
-      </c>
-      <c r="AK10">
-        <v>427.4</v>
-      </c>
-      <c r="AL10">
-        <v>323.2</v>
-      </c>
-      <c r="AM10">
-        <v>363.2</v>
-      </c>
-      <c r="AN10">
-        <v>406.3</v>
-      </c>
-      <c r="AO10">
-        <v>397.9</v>
-      </c>
-      <c r="AP10">
-        <v>332.6</v>
-      </c>
-      <c r="AQ10">
-        <v>382.1</v>
-      </c>
-      <c r="AR10">
-        <v>314.7</v>
-      </c>
-      <c r="AS10">
-        <v>348.4</v>
-      </c>
-      <c r="AT10">
-        <v>260</v>
-      </c>
-      <c r="AU10">
-        <v>303.2</v>
-      </c>
-      <c r="AV10">
-        <v>278.9</v>
-      </c>
-      <c r="AW10">
-        <v>128.4</v>
-      </c>
-      <c r="AX10">
         <v>0</v>
       </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:53">
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1129,431 +793,191 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>80</v>
+        <v>582.1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>88.40000000000001</v>
+        <v>612.6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>551.6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B5">
-        <v>88.40000000000001</v>
+        <v>515.8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6">
-        <v>88.40000000000001</v>
+        <v>550.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>82.09999999999999</v>
+        <v>427.4</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B8">
-        <v>84.2</v>
+        <v>323.2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>363.2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10">
-        <v>68.40000000000001</v>
+        <v>406.3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B11">
-        <v>61.1</v>
+        <v>397.9</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B12">
-        <v>68.40000000000001</v>
+        <v>332.6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B13">
-        <v>65.3</v>
+        <v>382.1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B14">
-        <v>73.7</v>
+        <v>314.7</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B15">
-        <v>97.90000000000001</v>
+        <v>348.4</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B16">
-        <v>112.6</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B17">
-        <v>154.7</v>
+        <v>303.2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B18">
-        <v>135.8</v>
+        <v>278.9</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B19">
-        <v>152.6</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20">
-        <v>168.4</v>
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21">
-        <v>153.7</v>
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22">
-        <v>150.5</v>
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23">
-        <v>238.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24">
-        <v>307.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25">
-        <v>277.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26">
-        <v>253.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27">
-        <v>217.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28">
-        <v>343.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30">
-        <v>621.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31">
-        <v>604.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32">
-        <v>582.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33">
-        <v>612.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34">
-        <v>551.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35">
-        <v>515.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36">
-        <v>550.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37">
-        <v>427.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38">
-        <v>323.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39">
-        <v>363.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40">
-        <v>406.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41">
-        <v>397.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42">
-        <v>332.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43">
-        <v>382.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44">
-        <v>314.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45">
-        <v>348.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>83</v>
-      </c>
-      <c r="B47">
-        <v>303.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48">
-        <v>278.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49">
-        <v>128.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>88</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
